--- a/Wusong/旧通信协议（用于武松）4-15.xlsx
+++ b/Wusong/旧通信协议（用于武松）4-15.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="22095" windowHeight="10065"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="123">
   <si>
     <t>安卓串口通信协议</t>
   </si>
@@ -239,6 +239,30 @@
   </si>
   <si>
     <t>数据低位(0-1)（0：触发，1：解除）</t>
+  </si>
+  <si>
+    <t>发送主次版本号</t>
+  </si>
+  <si>
+    <t>0x21</t>
+  </si>
+  <si>
+    <t>主版本号</t>
+  </si>
+  <si>
+    <t>次版本号</t>
+  </si>
+  <si>
+    <t>发送修改版本号</t>
+  </si>
+  <si>
+    <t>0x22</t>
+  </si>
+  <si>
+    <t>修改版本号</t>
+  </si>
+  <si>
+    <t>预留版本号</t>
   </si>
   <si>
     <t>安卓（Unity）→球盘</t>
@@ -354,6 +378,21 @@
   </si>
   <si>
     <t>力度</t>
+  </si>
+  <si>
+    <t>获取版本号</t>
+  </si>
+  <si>
+    <t>进入Bootloader</t>
+  </si>
+  <si>
+    <t>0xF0</t>
+  </si>
+  <si>
+    <t>0x42</t>
+  </si>
+  <si>
+    <t>0x4F</t>
   </si>
   <si>
     <t>停止所有输出</t>
@@ -788,7 +827,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -806,6 +845,15 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -935,7 +983,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
@@ -947,34 +995,34 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
@@ -1059,7 +1107,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1106,6 +1154,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1178,13 +1229,13 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>224790</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>69215</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>186690</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>130175</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1202,7 +1253,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13536295" y="7981315"/>
+          <a:off x="13536295" y="8489315"/>
           <a:ext cx="6134100" cy="4391660"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1469,7 +1520,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.1083333333333" style="1" customWidth="1"/>
@@ -2071,7 +2122,7 @@
       <c r="I26" s="14"/>
     </row>
     <row r="27" customHeight="1" spans="1:9">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="16" t="s">
         <v>67</v>
       </c>
       <c r="B27" s="14" t="s">
@@ -2094,118 +2145,118 @@
       <c r="I27" s="14"/>
     </row>
     <row r="28" customHeight="1" spans="1:9">
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
+      <c r="A28" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" s="14"/>
     </row>
     <row r="29" customHeight="1" spans="1:9">
-      <c r="A29" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
+      <c r="A29" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>77</v>
+      </c>
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
+      <c r="H29" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" s="14"/>
     </row>
     <row r="30" customHeight="1" spans="1:9">
-      <c r="A30" s="4" t="s">
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:9">
+      <c r="A31" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:9">
+      <c r="A32" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B32" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C32" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D32" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E32" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F30" s="8" t="s">
+      <c r="F32" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G30" s="8" t="s">
+      <c r="G32" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H30" s="5" t="s">
+      <c r="H32" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I30" s="14" t="s">
+      <c r="I32" s="14" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="31" customHeight="1" spans="1:9">
-      <c r="A31" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B31" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I31" s="14"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:9">
-      <c r="A32" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="E32" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" s="14"/>
     </row>
     <row r="33" customHeight="1" spans="1:9">
       <c r="A33" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="F33" s="14"/>
       <c r="G33" s="14"/>
@@ -2216,19 +2267,19 @@
     </row>
     <row r="34" customHeight="1" spans="1:9">
       <c r="A34" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B34" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="F34" s="14"/>
       <c r="G34" s="14"/>
@@ -2239,19 +2290,19 @@
     </row>
     <row r="35" customHeight="1" spans="1:9">
       <c r="A35" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B35" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="F35" s="14"/>
       <c r="G35" s="14"/>
@@ -2262,7 +2313,7 @@
     </row>
     <row r="36" customHeight="1" spans="1:9">
       <c r="A36" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B36" s="14" t="s">
         <v>10</v>
@@ -2271,10 +2322,10 @@
         <v>36</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F36" s="14"/>
       <c r="G36" s="14"/>
@@ -2285,69 +2336,65 @@
     </row>
     <row r="37" customHeight="1" spans="1:9">
       <c r="A37" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B37" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F37" s="14"/>
       <c r="G37" s="14"/>
       <c r="H37" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="I37" s="15" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="38" ht="41" customHeight="1" spans="1:9">
+      <c r="I37" s="14"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:9">
       <c r="A38" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B38" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="F38" s="14"/>
       <c r="G38" s="14"/>
       <c r="H38" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="I38" s="16" t="s">
-        <v>82</v>
-      </c>
+      <c r="I38" s="14"/>
     </row>
     <row r="39" customHeight="1" spans="1:9">
       <c r="A39" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D39" s="14" t="s">
         <v>11</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F39" s="14"/>
       <c r="G39" s="14"/>
@@ -2355,89 +2402,93 @@
         <v>15</v>
       </c>
       <c r="I39" s="15" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="1:9">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" ht="41" customHeight="1" spans="1:9">
       <c r="A40" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B40" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="F40" s="14"/>
       <c r="G40" s="14"/>
       <c r="H40" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="I40" s="16" t="s">
-        <v>88</v>
+      <c r="I40" s="17" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="1:9">
       <c r="A41" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B41" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="D41" s="14" t="s">
         <v>11</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="F41" s="14"/>
       <c r="G41" s="14"/>
       <c r="H41" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="I41" s="14"/>
+      <c r="I41" s="15" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="42" customHeight="1" spans="1:9">
       <c r="A42" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B42" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="F42" s="14"/>
       <c r="G42" s="14"/>
       <c r="H42" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="I42" s="14"/>
+      <c r="I42" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="43" customHeight="1" spans="1:9">
       <c r="A43" s="1" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B43" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D43" s="14" t="s">
         <v>11</v>
@@ -2454,19 +2505,19 @@
     </row>
     <row r="44" customHeight="1" spans="1:9">
       <c r="A44" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B44" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F44" s="14"/>
       <c r="G44" s="14"/>
@@ -2477,13 +2528,13 @@
     </row>
     <row r="45" customHeight="1" spans="1:9">
       <c r="A45" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B45" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D45" s="14" t="s">
         <v>11</v>
@@ -2500,13 +2551,13 @@
     </row>
     <row r="46" customHeight="1" spans="1:9">
       <c r="A46" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B46" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D46" s="14" t="s">
         <v>11</v>
@@ -2523,13 +2574,13 @@
     </row>
     <row r="47" customHeight="1" spans="1:9">
       <c r="A47" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B47" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D47" s="14" t="s">
         <v>11</v>
@@ -2546,19 +2597,19 @@
     </row>
     <row r="48" customHeight="1" spans="1:9">
       <c r="A48" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B48" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>104</v>
+        <v>11</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>105</v>
+        <v>11</v>
       </c>
       <c r="F48" s="14"/>
       <c r="G48" s="14"/>
@@ -2569,19 +2620,19 @@
     </row>
     <row r="49" customHeight="1" spans="1:9">
       <c r="A49" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B49" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>20</v>
+        <v>109</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>104</v>
+        <v>11</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="F49" s="14"/>
       <c r="G49" s="14"/>
@@ -2592,19 +2643,19 @@
     </row>
     <row r="50" customHeight="1" spans="1:9">
       <c r="A50" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B50" s="14" t="s">
         <v>10</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>11</v>
+        <v>112</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="F50" s="14"/>
       <c r="G50" s="14"/>
@@ -2612,14 +2663,106 @@
         <v>15</v>
       </c>
       <c r="I50" s="14"/>
+    </row>
+    <row r="51" customHeight="1" spans="1:9">
+      <c r="A51" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B51" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="E51" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I51" s="14"/>
+    </row>
+    <row r="52" customHeight="1" spans="1:9">
+      <c r="A52" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D52" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="E52" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I52" s="14"/>
+    </row>
+    <row r="53" customHeight="1" spans="1:9">
+      <c r="A53" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B53" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="D53" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="E53" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I53" s="14"/>
+    </row>
+    <row r="54" customHeight="1" spans="1:9">
+      <c r="A54" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B54" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C54" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="D54" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" s="14"/>
+      <c r="G54" s="14"/>
+      <c r="H54" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I54" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="B5:H5"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="B31:H31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Wusong/旧通信协议（用于武松）4-15.xlsx
+++ b/Wusong/旧通信协议（用于武松）4-15.xlsx
@@ -253,7 +253,7 @@
     <t>次版本号</t>
   </si>
   <si>
-    <t>发送修改版本号</t>
+    <t>发送修订版本号</t>
   </si>
   <si>
     <t>0x22</t>
